--- a/Piaui/2026/Julho/ResultadosTRI_3EM_LP/Simulado_III/EstItens_3EM_LP_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_LP/Simulado_III/EstItens_3EM_LP_S3.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -51,12 +51,6 @@
   </si>
   <si>
     <t xml:space="preserve">006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">008</t>
   </si>
   <si>
     <t xml:space="preserve">009</t>
@@ -470,19 +464,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>1.12276286497411</v>
+        <v>1.13633924571082</v>
       </c>
       <c r="C2" t="n">
-        <v>0.82961682326166</v>
+        <v>0.831356310653099</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0224552572994822</v>
+        <v>0.0227267849142165</v>
       </c>
       <c r="E2" t="n">
-        <v>291.480841163083</v>
+        <v>291.567815532655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.256950159427318</v>
+        <v>0.258211691431842</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -493,19 +487,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.400403982573578</v>
+        <v>0.400409323636589</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.02910080160809</v>
+        <v>-1.02892039872322</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00800807965147156</v>
+        <v>0.00800818647273179</v>
       </c>
       <c r="E3" t="n">
-        <v>198.544959919596</v>
+        <v>198.553980063839</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0204105413126267</v>
+        <v>0.0204481910852529</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -516,19 +510,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.236198540459054</v>
+        <v>0.234436944578408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00281997402003014</v>
+        <v>0.00432379812857425</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00472397080918108</v>
+        <v>0.00468873889156817</v>
       </c>
       <c r="E4" t="n">
-        <v>250.140998701002</v>
+        <v>250.216189906429</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0290032047827687</v>
+        <v>0.0289628757380641</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -539,19 +533,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>1.16546708410647</v>
+        <v>1.165353113681</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.673554761464892</v>
+        <v>-0.674191522242042</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0233093416821294</v>
+        <v>0.0233070622736201</v>
       </c>
       <c r="E5" t="n">
-        <v>216.322261926755</v>
+        <v>216.290423887898</v>
       </c>
       <c r="F5" t="n">
-        <v>0.116380103494649</v>
+        <v>0.116087754107005</v>
       </c>
       <c r="G5" t="s">
         <v>8</v>
@@ -562,19 +556,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>0.726443875684283</v>
+        <v>0.746960863908996</v>
       </c>
       <c r="C6" t="n">
-        <v>1.40763350728423</v>
+        <v>1.41275960532697</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0145288775136857</v>
+        <v>0.0149392172781799</v>
       </c>
       <c r="E6" t="n">
-        <v>320.381675364211</v>
+        <v>320.637980266348</v>
       </c>
       <c r="F6" t="n">
-        <v>0.179201840608295</v>
+        <v>0.183783110838929</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
@@ -585,19 +579,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>0.724963667143065</v>
+        <v>1.10477963638671</v>
       </c>
       <c r="C7" t="n">
-        <v>7.14728981128703</v>
+        <v>-1.47983046002032</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0144992733428613</v>
+        <v>0.0220955927277341</v>
       </c>
       <c r="E7" t="n">
-        <v>607.364490564352</v>
+        <v>176.008476998984</v>
       </c>
       <c r="F7" t="n">
-        <v>0.199455871406611</v>
+        <v>0.0355698451978264</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -608,19 +602,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>0.465987067478618</v>
+        <v>1.36450257976848</v>
       </c>
       <c r="C8" t="n">
-        <v>7.58865613072568</v>
+        <v>0.818209285042083</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00931974134957236</v>
+        <v>0.0272900515953695</v>
       </c>
       <c r="E8" t="n">
-        <v>629.432806536284</v>
+        <v>290.910464252104</v>
       </c>
       <c r="F8" t="n">
-        <v>0.125637906136926</v>
+        <v>0.144060241218673</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
@@ -631,19 +625,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>1.1054144594792</v>
+        <v>0.271634710523435</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.4797438125968</v>
+        <v>1.43072516060843</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0221082891895839</v>
+        <v>0.00543269421046869</v>
       </c>
       <c r="E9" t="n">
-        <v>176.01280937016</v>
+        <v>321.536258030422</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0356097062382465</v>
+        <v>0.0671279277921267</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
@@ -654,68 +648,68 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>1.35834020868194</v>
+        <v>1.31370481608545</v>
       </c>
       <c r="C10" t="n">
-        <v>0.818213564411749</v>
+        <v>-0.968423168030581</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0271668041736388</v>
+        <v>0.0262740963217091</v>
       </c>
       <c r="E10" t="n">
-        <v>290.910678220587</v>
+        <v>201.578841598471</v>
       </c>
       <c r="F10" t="n">
-        <v>0.14366229585265</v>
+        <v>0.036676474322631</v>
       </c>
       <c r="G10" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.08556921188172</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.54783058346452</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0217113842376344</v>
+      </c>
+      <c r="E11" t="n">
+        <v>222.608470826774</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0202347578937095</v>
+      </c>
+      <c r="G11" t="s">
         <v>17</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.270361654429384</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.42540559988881</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.00540723308858768</v>
-      </c>
-      <c r="E11" t="n">
-        <v>321.27027999444</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.0659172101613634</v>
-      </c>
-      <c r="G11" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1.31370481608546</v>
+        <v>0.65</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.968423168030579</v>
+        <v>0.85664</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0262740963217091</v>
+        <v>0.013</v>
       </c>
       <c r="E12" t="n">
-        <v>201.578841598471</v>
+        <v>292.832</v>
       </c>
       <c r="F12" t="n">
-        <v>0.036676474322631</v>
+        <v>0.087</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -723,22 +717,22 @@
         <v>20</v>
       </c>
       <c r="B13" t="n">
-        <v>1.08556921188172</v>
+        <v>1.16969965028707</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.54783058346452</v>
+        <v>-1.0259137823486</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0217113842376344</v>
+        <v>0.0233939930057413</v>
       </c>
       <c r="E13" t="n">
-        <v>222.608470826774</v>
+        <v>198.70431088257</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0202347578937095</v>
+        <v>0.0584035481136804</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -746,22 +740,22 @@
         <v>21</v>
       </c>
       <c r="B14" t="n">
-        <v>0.65</v>
+        <v>0.601247426572951</v>
       </c>
       <c r="C14" t="n">
-        <v>0.85664</v>
+        <v>1.95572223672419</v>
       </c>
       <c r="D14" t="n">
-        <v>0.013</v>
+        <v>0.012024948531459</v>
       </c>
       <c r="E14" t="n">
-        <v>292.832</v>
+        <v>347.78611183621</v>
       </c>
       <c r="F14" t="n">
-        <v>0.087</v>
+        <v>0.0743605832762184</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -769,19 +763,19 @@
         <v>22</v>
       </c>
       <c r="B15" t="n">
-        <v>1.17198804048928</v>
+        <v>0.896357059768843</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.02391498712326</v>
+        <v>-0.197574761300658</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0234397608097856</v>
+        <v>0.0179271411953769</v>
       </c>
       <c r="E15" t="n">
-        <v>198.804250643837</v>
+        <v>240.121261934967</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0590869104879992</v>
+        <v>0.08841015762089</v>
       </c>
       <c r="G15" t="s">
         <v>8</v>
@@ -792,19 +786,19 @@
         <v>23</v>
       </c>
       <c r="B16" t="n">
-        <v>0.612980643789786</v>
+        <v>1.11844928707211</v>
       </c>
       <c r="C16" t="n">
-        <v>1.94941082995017</v>
+        <v>0.685626420800364</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0122596128757957</v>
+        <v>0.0223689857414422</v>
       </c>
       <c r="E16" t="n">
-        <v>347.470541497509</v>
+        <v>284.281321040018</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0771367986575117</v>
+        <v>0.138937469552852</v>
       </c>
       <c r="G16" t="s">
         <v>8</v>
@@ -815,22 +809,22 @@
         <v>24</v>
       </c>
       <c r="B17" t="n">
-        <v>0.902498255568884</v>
+        <v>0.6</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.18911201103878</v>
+        <v>2.80222</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0180499651113777</v>
+        <v>0.012</v>
       </c>
       <c r="E17" t="n">
-        <v>240.544399448061</v>
+        <v>390.111</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0908030584899293</v>
+        <v>0.107</v>
       </c>
       <c r="G17" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -838,19 +832,19 @@
         <v>25</v>
       </c>
       <c r="B18" t="n">
-        <v>1.11016206602146</v>
+        <v>0.891563570635083</v>
       </c>
       <c r="C18" t="n">
-        <v>0.685158712212912</v>
+        <v>1.69046648496053</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0222032413204291</v>
+        <v>0.0178312714127017</v>
       </c>
       <c r="E18" t="n">
-        <v>284.257935610646</v>
+        <v>334.523324248027</v>
       </c>
       <c r="F18" t="n">
-        <v>0.138191849324986</v>
+        <v>0.168868392695792</v>
       </c>
       <c r="G18" t="s">
         <v>8</v>
@@ -861,22 +855,22 @@
         <v>26</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6</v>
+        <v>1.07129526272003</v>
       </c>
       <c r="C19" t="n">
-        <v>2.80222</v>
+        <v>-0.112645049660066</v>
       </c>
       <c r="D19" t="n">
-        <v>0.012</v>
+        <v>0.0214259052544006</v>
       </c>
       <c r="E19" t="n">
-        <v>390.111</v>
+        <v>244.367747516997</v>
       </c>
       <c r="F19" t="n">
-        <v>0.107</v>
+        <v>0.168953824277196</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -884,19 +878,19 @@
         <v>27</v>
       </c>
       <c r="B20" t="n">
-        <v>0.890971065081044</v>
+        <v>1.66316221830154</v>
       </c>
       <c r="C20" t="n">
-        <v>1.69233713983014</v>
+        <v>0.719786442837438</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0178194213016209</v>
+        <v>0.0332632443660308</v>
       </c>
       <c r="E20" t="n">
-        <v>334.616856991507</v>
+        <v>285.989322141872</v>
       </c>
       <c r="F20" t="n">
-        <v>0.168941718238344</v>
+        <v>0.235056095367823</v>
       </c>
       <c r="G20" t="s">
         <v>8</v>
@@ -907,22 +901,22 @@
         <v>28</v>
       </c>
       <c r="B21" t="n">
-        <v>1.06716432220288</v>
+        <v>0.78482076420473</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.116335131444122</v>
+        <v>0.99309028021504</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0213432864440576</v>
+        <v>0.0156964152840946</v>
       </c>
       <c r="E21" t="n">
-        <v>244.183243427794</v>
+        <v>299.654514010752</v>
       </c>
       <c r="F21" t="n">
-        <v>0.167928028856595</v>
+        <v>0.178494837460805</v>
       </c>
       <c r="G21" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -930,22 +924,22 @@
         <v>29</v>
       </c>
       <c r="B22" t="n">
-        <v>1.64343754889374</v>
+        <v>0.84445725224476</v>
       </c>
       <c r="C22" t="n">
-        <v>0.71903784236781</v>
+        <v>1.66650434769532</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0328687509778747</v>
+        <v>0.0168891450448952</v>
       </c>
       <c r="E22" t="n">
-        <v>285.951892118391</v>
+        <v>333.325217384766</v>
       </c>
       <c r="F22" t="n">
-        <v>0.23427875453806</v>
+        <v>0.214157847906194</v>
       </c>
       <c r="G22" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -953,22 +947,22 @@
         <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>0.78482076420473</v>
+        <v>0.55</v>
       </c>
       <c r="C23" t="n">
-        <v>0.993090280215039</v>
+        <v>-0.503840000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0156964152840946</v>
+        <v>0.011</v>
       </c>
       <c r="E23" t="n">
-        <v>299.654514010752</v>
+        <v>224.808</v>
       </c>
       <c r="F23" t="n">
-        <v>0.178494837460805</v>
+        <v>0.015</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -976,68 +970,22 @@
         <v>31</v>
       </c>
       <c r="B24" t="n">
-        <v>0.84445725224476</v>
+        <v>1.05</v>
       </c>
       <c r="C24" t="n">
-        <v>1.66650434769532</v>
+        <v>-0.636720000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0168891450448952</v>
+        <v>0.021</v>
       </c>
       <c r="E24" t="n">
-        <v>333.325217384766</v>
+        <v>218.164</v>
       </c>
       <c r="F24" t="n">
-        <v>0.214157847906194</v>
+        <v>0.0649999999999999</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.503839999999999</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="E25" t="n">
-        <v>224.808</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.63672</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E26" t="n">
-        <v>218.164</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="G26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
